--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B2" t="n">
         <v>90964</v>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R2" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B3" t="n">
         <v>90964</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R3" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B2" t="n">
         <v>90964</v>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R2" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B3" t="n">
         <v>90964</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R3" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R2" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R3" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B2" t="n">
         <v>90972</v>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R2" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B3" t="n">
         <v>90972</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R3" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R2" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R3" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B2" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R2" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R3" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,1005 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123505892</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579235</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6436895</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123505926</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579286</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6436826</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123505938</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579281</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6436823</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123505971</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105482</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579314</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6436813</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123505983</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579312</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6436787</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123506011</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579366</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6436697</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123505885</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579245</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6436903</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123505961</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579309</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6436810</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123506000</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579358</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6436698</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R2" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R3" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505892</v>
+        <v>123505885</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579235</v>
+        <v>579245</v>
       </c>
       <c r="R4" t="n">
-        <v>6436895</v>
+        <v>6436903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123505926</v>
+        <v>123506000</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,39 +1026,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579286</v>
+        <v>579358</v>
       </c>
       <c r="R5" t="n">
-        <v>6436826</v>
+        <v>6436698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505938</v>
+        <v>123505926</v>
       </c>
       <c r="B6" t="n">
         <v>98376</v>
@@ -1161,7 +1157,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579281</v>
+        <v>579286</v>
       </c>
       <c r="R6" t="n">
-        <v>6436823</v>
+        <v>6436826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505971</v>
+        <v>123505938</v>
       </c>
       <c r="B7" t="n">
-        <v>105482</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579314</v>
+        <v>579281</v>
       </c>
       <c r="R7" t="n">
-        <v>6436813</v>
+        <v>6436823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123506011</v>
+        <v>123505892</v>
       </c>
       <c r="B9" t="n">
         <v>90983</v>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579366</v>
+        <v>579235</v>
       </c>
       <c r="R9" t="n">
-        <v>6436697</v>
+        <v>6436895</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123505885</v>
+        <v>123505961</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,35 +1583,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579245</v>
+        <v>579309</v>
       </c>
       <c r="R10" t="n">
-        <v>6436903</v>
+        <v>6436810</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123505961</v>
+        <v>123506011</v>
       </c>
       <c r="B11" t="n">
         <v>90983</v>
@@ -1729,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579309</v>
+        <v>579366</v>
       </c>
       <c r="R11" t="n">
-        <v>6436810</v>
+        <v>6436697</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123506000</v>
+        <v>123505971</v>
       </c>
       <c r="B12" t="n">
-        <v>90983</v>
+        <v>105482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,34 +1803,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579358</v>
+        <v>579314</v>
       </c>
       <c r="R12" t="n">
-        <v>6436698</v>
+        <v>6436813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872819</v>
+        <v>122872834</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>90986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579365</v>
+        <v>579367</v>
       </c>
       <c r="R2" t="n">
-        <v>6436698</v>
+        <v>6436692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872834</v>
+        <v>122872819</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579367</v>
+        <v>579365</v>
       </c>
       <c r="R3" t="n">
-        <v>6436692</v>
+        <v>6436698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505885</v>
+        <v>123505938</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579245</v>
+        <v>579281</v>
       </c>
       <c r="R4" t="n">
-        <v>6436903</v>
+        <v>6436823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123506000</v>
+        <v>123505885</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,34 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579358</v>
+        <v>579245</v>
       </c>
       <c r="R5" t="n">
-        <v>6436698</v>
+        <v>6436903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505926</v>
+        <v>123506011</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>90986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,39 +1137,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579286</v>
+        <v>579366</v>
       </c>
       <c r="R6" t="n">
-        <v>6436826</v>
+        <v>6436697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505938</v>
+        <v>123506000</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,35 +1247,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579281</v>
+        <v>579358</v>
       </c>
       <c r="R7" t="n">
-        <v>6436823</v>
+        <v>6436698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505983</v>
+        <v>123505961</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>90986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,35 +1357,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579312</v>
+        <v>579309</v>
       </c>
       <c r="R8" t="n">
-        <v>6436787</v>
+        <v>6436810</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123505892</v>
+        <v>123505926</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1467,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579235</v>
+        <v>579286</v>
       </c>
       <c r="R9" t="n">
-        <v>6436895</v>
+        <v>6436826</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123505961</v>
+        <v>123505983</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>98379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,34 +1582,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579309</v>
+        <v>579312</v>
       </c>
       <c r="R10" t="n">
-        <v>6436810</v>
+        <v>6436787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123506011</v>
+        <v>123505892</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>90986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579366</v>
+        <v>579235</v>
       </c>
       <c r="R11" t="n">
-        <v>6436697</v>
+        <v>6436895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1794,7 @@
         <v>123505971</v>
       </c>
       <c r="B12" t="n">
-        <v>105482</v>
+        <v>105485</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505938</v>
+        <v>123506000</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>91003</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +915,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579281</v>
+        <v>579358</v>
       </c>
       <c r="R4" t="n">
-        <v>6436823</v>
+        <v>6436698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123505885</v>
+        <v>123505971</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579245</v>
+        <v>579314</v>
       </c>
       <c r="R5" t="n">
-        <v>6436903</v>
+        <v>6436813</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123506011</v>
+        <v>123505892</v>
       </c>
       <c r="B6" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579366</v>
+        <v>579235</v>
       </c>
       <c r="R6" t="n">
-        <v>6436697</v>
+        <v>6436895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123506000</v>
+        <v>123505983</v>
       </c>
       <c r="B7" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,34 +1246,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579358</v>
+        <v>579312</v>
       </c>
       <c r="R7" t="n">
-        <v>6436698</v>
+        <v>6436787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505961</v>
+        <v>123505885</v>
       </c>
       <c r="B8" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1357,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579309</v>
+        <v>579245</v>
       </c>
       <c r="R8" t="n">
-        <v>6436810</v>
+        <v>6436903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123505926</v>
+        <v>123505961</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>91003</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,39 +1468,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579286</v>
+        <v>579309</v>
       </c>
       <c r="R9" t="n">
-        <v>6436826</v>
+        <v>6436810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123505983</v>
+        <v>123506011</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>91003</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,35 +1578,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579312</v>
+        <v>579366</v>
       </c>
       <c r="R10" t="n">
-        <v>6436787</v>
+        <v>6436697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123505892</v>
+        <v>123505926</v>
       </c>
       <c r="B11" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,34 +1688,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579235</v>
+        <v>579286</v>
       </c>
       <c r="R11" t="n">
-        <v>6436895</v>
+        <v>6436826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123505971</v>
+        <v>123505938</v>
       </c>
       <c r="B12" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,25 +1803,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579314</v>
+        <v>579281</v>
       </c>
       <c r="R12" t="n">
-        <v>6436813</v>
+        <v>6436823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123506000</v>
+        <v>123505885</v>
       </c>
       <c r="B4" t="n">
-        <v>91003</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579358</v>
+        <v>579245</v>
       </c>
       <c r="R4" t="n">
-        <v>6436698</v>
+        <v>6436903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123505971</v>
+        <v>123505926</v>
       </c>
       <c r="B5" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,28 +1026,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579314</v>
+        <v>579286</v>
       </c>
       <c r="R5" t="n">
-        <v>6436813</v>
+        <v>6436826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505892</v>
+        <v>123505961</v>
       </c>
       <c r="B6" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579235</v>
+        <v>579309</v>
       </c>
       <c r="R6" t="n">
-        <v>6436895</v>
+        <v>6436810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505983</v>
+        <v>123505938</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579312</v>
+        <v>579281</v>
       </c>
       <c r="R7" t="n">
-        <v>6436787</v>
+        <v>6436823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505885</v>
+        <v>123505892</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,35 +1362,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579245</v>
+        <v>579235</v>
       </c>
       <c r="R8" t="n">
-        <v>6436903</v>
+        <v>6436895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123505961</v>
+        <v>123505971</v>
       </c>
       <c r="B9" t="n">
-        <v>91003</v>
+        <v>105518</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,34 +1472,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579309</v>
+        <v>579314</v>
       </c>
       <c r="R9" t="n">
-        <v>6436810</v>
+        <v>6436813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123506011</v>
+        <v>123505983</v>
       </c>
       <c r="B10" t="n">
-        <v>91003</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,34 +1583,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1613,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579366</v>
+        <v>579312</v>
       </c>
       <c r="R10" t="n">
-        <v>6436697</v>
+        <v>6436787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123505926</v>
+        <v>123506000</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,39 +1694,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579286</v>
+        <v>579358</v>
       </c>
       <c r="R11" t="n">
-        <v>6436826</v>
+        <v>6436698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123505938</v>
+        <v>123506011</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,35 +1804,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579281</v>
+        <v>579366</v>
       </c>
       <c r="R12" t="n">
-        <v>6436823</v>
+        <v>6436697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505885</v>
+        <v>123505971</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579245</v>
+        <v>579314</v>
       </c>
       <c r="R4" t="n">
-        <v>6436903</v>
+        <v>6436813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123505926</v>
+        <v>123505983</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,11 +1047,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1066,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579286</v>
+        <v>579312</v>
       </c>
       <c r="R5" t="n">
-        <v>6436826</v>
+        <v>6436787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,17 +1118,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505961</v>
+        <v>123505938</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,34 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579309</v>
+        <v>579281</v>
       </c>
       <c r="R6" t="n">
-        <v>6436810</v>
+        <v>6436823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505938</v>
+        <v>123506000</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>91010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,35 +1248,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579281</v>
+        <v>579358</v>
       </c>
       <c r="R7" t="n">
-        <v>6436823</v>
+        <v>6436698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,17 +1339,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505892</v>
+        <v>123506011</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579235</v>
+        <v>579366</v>
       </c>
       <c r="R8" t="n">
-        <v>6436895</v>
+        <v>6436697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,17 +1449,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123505971</v>
+        <v>123505961</v>
       </c>
       <c r="B9" t="n">
-        <v>105518</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,35 +1468,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579314</v>
+        <v>579309</v>
       </c>
       <c r="R9" t="n">
-        <v>6436813</v>
+        <v>6436810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,17 +1559,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123505983</v>
+        <v>123505892</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>91010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,35 +1578,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579312</v>
+        <v>579235</v>
       </c>
       <c r="R10" t="n">
-        <v>6436787</v>
+        <v>6436895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,10 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123506000</v>
+        <v>123505926</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,34 +1688,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1729,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579358</v>
+        <v>579286</v>
       </c>
       <c r="R11" t="n">
-        <v>6436698</v>
+        <v>6436826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123506011</v>
+        <v>123505885</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,34 +1803,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579366</v>
+        <v>579245</v>
       </c>
       <c r="R12" t="n">
-        <v>6436697</v>
+        <v>6436903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505971</v>
+        <v>123505892</v>
       </c>
       <c r="B4" t="n">
-        <v>105520</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +915,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579314</v>
+        <v>579235</v>
       </c>
       <c r="R4" t="n">
-        <v>6436813</v>
+        <v>6436895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,17 +1006,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123505983</v>
+        <v>123506000</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,35 +1025,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579312</v>
+        <v>579358</v>
       </c>
       <c r="R5" t="n">
-        <v>6436787</v>
+        <v>6436698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,17 +1116,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505938</v>
+        <v>123505926</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,7 +1156,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1173,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579281</v>
+        <v>579286</v>
       </c>
       <c r="R6" t="n">
-        <v>6436823</v>
+        <v>6436826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123506000</v>
+        <v>123505885</v>
       </c>
       <c r="B7" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,34 +1250,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579358</v>
+        <v>579245</v>
       </c>
       <c r="R7" t="n">
-        <v>6436698</v>
+        <v>6436903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,17 +1342,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123506011</v>
+        <v>123505983</v>
       </c>
       <c r="B8" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,34 +1361,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579366</v>
+        <v>579312</v>
       </c>
       <c r="R8" t="n">
-        <v>6436697</v>
+        <v>6436787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1453,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1559,14 +1563,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123505892</v>
+        <v>123506011</v>
       </c>
       <c r="B10" t="n">
         <v>91010</v>
@@ -1613,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579235</v>
+        <v>579366</v>
       </c>
       <c r="R10" t="n">
-        <v>6436895</v>
+        <v>6436697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123505926</v>
+        <v>123505938</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,11 +1713,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579286</v>
+        <v>579281</v>
       </c>
       <c r="R11" t="n">
-        <v>6436826</v>
+        <v>6436823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123505885</v>
+        <v>123505971</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,25 +1803,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579245</v>
+        <v>579314</v>
       </c>
       <c r="R12" t="n">
-        <v>6436903</v>
+        <v>6436813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123506000</v>
+        <v>123506011</v>
       </c>
       <c r="B5" t="n">
         <v>91010</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579358</v>
+        <v>579366</v>
       </c>
       <c r="R5" t="n">
-        <v>6436698</v>
+        <v>6436697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505926</v>
+        <v>123505971</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,32 +1135,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1175,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579286</v>
+        <v>579314</v>
       </c>
       <c r="R6" t="n">
-        <v>6436826</v>
+        <v>6436813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505885</v>
+        <v>123505983</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1286,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579245</v>
+        <v>579312</v>
       </c>
       <c r="R7" t="n">
-        <v>6436903</v>
+        <v>6436787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505983</v>
+        <v>123505938</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1397,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579312</v>
+        <v>579281</v>
       </c>
       <c r="R8" t="n">
-        <v>6436787</v>
+        <v>6436823</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1456,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123505961</v>
+        <v>123506000</v>
       </c>
       <c r="B9" t="n">
         <v>91010</v>
@@ -1507,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579309</v>
+        <v>579358</v>
       </c>
       <c r="R9" t="n">
-        <v>6436810</v>
+        <v>6436698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123506011</v>
+        <v>123505961</v>
       </c>
       <c r="B10" t="n">
         <v>91010</v>
@@ -1617,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579366</v>
+        <v>579309</v>
       </c>
       <c r="R10" t="n">
-        <v>6436697</v>
+        <v>6436810</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1676,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123505938</v>
+        <v>123505926</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1713,7 +1709,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579281</v>
+        <v>579286</v>
       </c>
       <c r="R11" t="n">
-        <v>6436823</v>
+        <v>6436826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123505971</v>
+        <v>123505885</v>
       </c>
       <c r="B12" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,25 +1803,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579314</v>
+        <v>579245</v>
       </c>
       <c r="R12" t="n">
-        <v>6436813</v>
+        <v>6436903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505892</v>
+        <v>123505926</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579235</v>
+        <v>579286</v>
       </c>
       <c r="R4" t="n">
-        <v>6436895</v>
+        <v>6436826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123506011</v>
+        <v>123505885</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,34 +1030,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579366</v>
+        <v>579245</v>
       </c>
       <c r="R5" t="n">
-        <v>6436697</v>
+        <v>6436903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505971</v>
+        <v>123505961</v>
       </c>
       <c r="B6" t="n">
-        <v>105095</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,35 +1141,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579314</v>
+        <v>579309</v>
       </c>
       <c r="R6" t="n">
-        <v>6436813</v>
+        <v>6436810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505983</v>
+        <v>123505892</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,35 +1251,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579312</v>
+        <v>579235</v>
       </c>
       <c r="R7" t="n">
-        <v>6436787</v>
+        <v>6436895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505938</v>
+        <v>123505971</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,25 +1361,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579281</v>
+        <v>579314</v>
       </c>
       <c r="R8" t="n">
-        <v>6436823</v>
+        <v>6436813</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123506000</v>
+        <v>123505983</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,34 +1472,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579358</v>
+        <v>579312</v>
       </c>
       <c r="R9" t="n">
-        <v>6436698</v>
+        <v>6436787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123505961</v>
+        <v>123506011</v>
       </c>
       <c r="B10" t="n">
         <v>91010</v>
@@ -1613,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579309</v>
+        <v>579366</v>
       </c>
       <c r="R10" t="n">
-        <v>6436810</v>
+        <v>6436697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123505926</v>
+        <v>123506000</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,39 +1693,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579286</v>
+        <v>579358</v>
       </c>
       <c r="R11" t="n">
-        <v>6436826</v>
+        <v>6436698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123505885</v>
+        <v>123505938</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579245</v>
+        <v>579281</v>
       </c>
       <c r="R12" t="n">
-        <v>6436903</v>
+        <v>6436823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505926</v>
+        <v>123505983</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -936,11 +936,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -955,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579286</v>
+        <v>579312</v>
       </c>
       <c r="R4" t="n">
-        <v>6436826</v>
+        <v>6436787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,17 +1007,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123505885</v>
+        <v>123505892</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,35 +1026,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579245</v>
+        <v>579235</v>
       </c>
       <c r="R5" t="n">
-        <v>6436903</v>
+        <v>6436895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123505961</v>
+        <v>123506000</v>
       </c>
       <c r="B6" t="n">
         <v>91010</v>
@@ -1176,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579309</v>
+        <v>579358</v>
       </c>
       <c r="R6" t="n">
-        <v>6436810</v>
+        <v>6436698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,17 +1227,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505892</v>
+        <v>123505926</v>
       </c>
       <c r="B7" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1246,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579235</v>
+        <v>579286</v>
       </c>
       <c r="R7" t="n">
-        <v>6436895</v>
+        <v>6436826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505971</v>
+        <v>123506011</v>
       </c>
       <c r="B8" t="n">
-        <v>105095</v>
+        <v>91010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,35 +1361,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1397,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579314</v>
+        <v>579366</v>
       </c>
       <c r="R8" t="n">
-        <v>6436813</v>
+        <v>6436697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,17 +1452,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123505983</v>
+        <v>123505971</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579312</v>
+        <v>579314</v>
       </c>
       <c r="R9" t="n">
-        <v>6436787</v>
+        <v>6436813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,17 +1563,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123506011</v>
+        <v>123505938</v>
       </c>
       <c r="B10" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,34 +1582,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579366</v>
+        <v>579281</v>
       </c>
       <c r="R10" t="n">
-        <v>6436697</v>
+        <v>6436823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123506000</v>
+        <v>123505961</v>
       </c>
       <c r="B11" t="n">
         <v>91010</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579358</v>
+        <v>579309</v>
       </c>
       <c r="R11" t="n">
-        <v>6436698</v>
+        <v>6436810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,14 +1784,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123505938</v>
+        <v>123505885</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579281</v>
+        <v>579245</v>
       </c>
       <c r="R12" t="n">
-        <v>6436823</v>
+        <v>6436903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123506011</v>
+        <v>123505971</v>
       </c>
       <c r="B8" t="n">
-        <v>91010</v>
+        <v>105095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,34 +1361,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579366</v>
+        <v>579314</v>
       </c>
       <c r="R8" t="n">
-        <v>6436697</v>
+        <v>6436813</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123505971</v>
+        <v>123506011</v>
       </c>
       <c r="B9" t="n">
-        <v>105095</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,35 +1472,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579314</v>
+        <v>579366</v>
       </c>
       <c r="R9" t="n">
-        <v>6436813</v>
+        <v>6436697</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 3429-2024 artfynd.xlsx
+++ b/artfynd/A 3429-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123505983</v>
+        <v>123505892</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +915,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579312</v>
+        <v>579235</v>
       </c>
       <c r="R4" t="n">
-        <v>6436787</v>
+        <v>6436895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,17 +1006,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123505892</v>
+        <v>123505938</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,34 +1025,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579235</v>
+        <v>579281</v>
       </c>
       <c r="R5" t="n">
-        <v>6436895</v>
+        <v>6436823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123505926</v>
+        <v>123505971</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,32 +1246,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1286,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579286</v>
+        <v>579314</v>
       </c>
       <c r="R7" t="n">
-        <v>6436826</v>
+        <v>6436813</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,17 +1338,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123505971</v>
+        <v>123505885</v>
       </c>
       <c r="B8" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,25 +1357,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579314</v>
+        <v>579245</v>
       </c>
       <c r="R8" t="n">
-        <v>6436813</v>
+        <v>6436903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,17 +1449,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123506011</v>
+        <v>123505926</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,34 +1468,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579366</v>
+        <v>579286</v>
       </c>
       <c r="R9" t="n">
-        <v>6436697</v>
+        <v>6436826</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,17 +1564,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123505938</v>
+        <v>123506011</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,35 +1583,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579281</v>
+        <v>579366</v>
       </c>
       <c r="R10" t="n">
-        <v>6436823</v>
+        <v>6436697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,17 +1674,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123505961</v>
+        <v>123505983</v>
       </c>
       <c r="B11" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,34 +1693,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579309</v>
+        <v>579312</v>
       </c>
       <c r="R11" t="n">
-        <v>6436810</v>
+        <v>6436787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123505885</v>
+        <v>123505961</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,35 +1804,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579245</v>
+        <v>579309</v>
       </c>
       <c r="R12" t="n">
-        <v>6436903</v>
+        <v>6436810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
